--- a/Assets/Config/Excel/GlobalLocalizationConfigExcel.xlsx
+++ b/Assets/Config/Excel/GlobalLocalizationConfigExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Projects\Joker_MMO\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9962200E-806D-4BF8-809B-F79E93014332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A32EBD-065A-41A0-8185-F20B90098E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-1032" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31884" yWindow="1860" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Config/Excel/GlobalLocalizationConfigExcel.xlsx
+++ b/Assets/Config/Excel/GlobalLocalizationConfigExcel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Projects\Joker_MMO\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A32EBD-065A-41A0-8185-F20B90098E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4865A9-8834-4C38-B6F8-B90D92B26C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31884" yWindow="1860" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3444" yWindow="1488" windowWidth="23040" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>Key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,6 +120,20 @@
   </si>
   <si>
     <t>用户重复登录，您已被强制下线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>背包空间不足</t>
+  </si>
+  <si>
+    <t>金币不足</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缺少材料</t>
+  </si>
+  <si>
+    <t>缺少材料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -445,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65" customWidth="1"/>
@@ -584,6 +598,30 @@
         <v>23</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
